--- a/data/vip2022.xlsx
+++ b/data/vip2022.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11102"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/isabelhaas/Documents/Coding/aytogermany/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACA467B5-16C6-F341-AD44-AA44F9DEE307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="480" yWindow="680" windowWidth="26700" windowHeight="13300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Nights"/>
+    <sheet name="Nights" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="22">
   <si>
     <t>Anna</t>
   </si>
@@ -85,8 +91,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -150,41 +155,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -195,10 +194,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -236,71 +235,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -328,7 +327,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -351,11 +350,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -364,13 +363,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -380,7 +379,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -389,7 +388,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -398,7 +397,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -406,10 +405,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -474,29 +473,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="12.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="11" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1"/>
+    <row r="1" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
@@ -531,345 +520,383 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18">
+    <row r="2" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="4">
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18">
+    <row r="3" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" t="s">
         <v>16</v>
       </c>
-      <c r="L3" s="5">
+      <c r="L3" s="4">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18">
+    <row r="4" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" t="s">
         <v>14</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L4" s="4">
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18">
+    <row r="5" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="4" t="s">
+      <c r="J5" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="4" t="s">
+      <c r="K5" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L5" s="5">
+      <c r="L5" s="4">
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18">
+    <row r="6" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>4</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="F6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="H6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" t="s">
         <v>20</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L6" s="4">
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18">
+    <row r="7" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>5</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="J7" t="s">
         <v>17</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" t="s">
         <v>20</v>
       </c>
-      <c r="L7" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18">
+      <c r="L7" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>6</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="L8" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18">
+      <c r="L8" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>7</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" t="s">
         <v>13</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="J9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K9" t="s">
         <v>19</v>
       </c>
-      <c r="K9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L9" s="5">
-        <v>7</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="L9" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>8</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="I10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" t="s">
+        <v>19</v>
+      </c>
+      <c r="K10" t="s">
+        <v>17</v>
+      </c>
+      <c r="L10" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" t="s">
         <v>21</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H11" t="s">
         <v>20</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I11" t="s">
         <v>16</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="J11" t="s">
         <v>19</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K11" t="s">
         <v>17</v>
       </c>
-      <c r="L10" s="5">
+      <c r="L11" s="4">
         <v>10</v>
       </c>
     </row>

--- a/data/vip2022.xlsx
+++ b/data/vip2022.xlsx
@@ -1,26 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11102"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/isabelhaas/Documents/Coding/aytogermany/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACA467B5-16C6-F341-AD44-AA44F9DEE307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="680" windowWidth="26700" windowHeight="13300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Nights" sheetId="1" r:id="rId1"/>
+    <sheet name="Candidates" sheetId="1" r:id="rId1"/>
+    <sheet name="Nights" sheetId="2" r:id="rId2"/>
+    <sheet name="Matchboxes" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="27">
+  <si>
+    <t>left</t>
+  </si>
+  <si>
+    <t>right</t>
+  </si>
+  <si>
+    <t>mm</t>
+  </si>
   <si>
     <t>Anna</t>
   </si>
@@ -52,47 +57,53 @@
     <t>Zoe</t>
   </si>
   <si>
+    <t>Amadu</t>
+  </si>
+  <si>
+    <t>Calvin</t>
+  </si>
+  <si>
+    <t>Fabio</t>
+  </si>
+  <si>
+    <t>Luca</t>
+  </si>
+  <si>
+    <t>Lukas</t>
+  </si>
+  <si>
+    <t>Martin</t>
+  </si>
+  <si>
+    <t>Maurice</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Michael</t>
+  </si>
+  <si>
+    <t>Pharrell</t>
+  </si>
+  <si>
+    <t>Felix</t>
+  </si>
+  <si>
     <t>lights</t>
   </si>
   <si>
-    <t>Michael</t>
-  </si>
-  <si>
-    <t>Amadu</t>
-  </si>
-  <si>
-    <t>Martin</t>
-  </si>
-  <si>
-    <t>Max</t>
-  </si>
-  <si>
-    <t>Calvin</t>
-  </si>
-  <si>
-    <t>Lukas</t>
-  </si>
-  <si>
-    <t>Pharrell</t>
-  </si>
-  <si>
-    <t>Fabio</t>
-  </si>
-  <si>
-    <t>Maurice</t>
-  </si>
-  <si>
-    <t>Luca</t>
-  </si>
-  <si>
-    <t>Felix</t>
+    <t>episode</t>
+  </si>
+  <si>
+    <t>result</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -101,49 +112,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5C6C7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -155,22 +146,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -178,14 +157,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -264,7 +235,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -299,7 +269,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -323,6 +292,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
@@ -333,31 +303,31 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="51000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="94000"/>
+                <a:shade val="94000"/>
                 <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="9500"/>
+              <a:shade val="95000"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
@@ -379,7 +349,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -437,7 +407,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="20000"/>
+                <a:shade val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -450,12 +420,13 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
                 <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
+                <a:shade val="30000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -473,431 +444,675 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:L11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="11" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
-        <v>0</v>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="11" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
       </c>
       <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
         <v>15</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
         <v>16</v>
       </c>
-      <c r="H2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="K2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
         <v>18</v>
       </c>
-      <c r="J2" t="s">
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" t="s">
         <v>19</v>
       </c>
-      <c r="K2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="J3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
         <v>18</v>
-      </c>
-      <c r="I3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L3" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
-        <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
         <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L4" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
-        <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s">
         <v>18</v>
       </c>
-      <c r="E5" t="s">
+      <c r="H6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" t="s">
         <v>16</v>
       </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="K6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" t="s">
         <v>20</v>
       </c>
-      <c r="H5" t="s">
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
         <v>15</v>
       </c>
-      <c r="I5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
+      <c r="H8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" t="s">
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
         <v>21</v>
       </c>
-      <c r="G6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="B9" t="s">
         <v>13</v>
       </c>
-      <c r="I6" t="s">
+      <c r="C9" t="s">
         <v>16</v>
       </c>
-      <c r="J6" t="s">
+      <c r="D9" t="s">
         <v>14</v>
-      </c>
-      <c r="K6" t="s">
-        <v>20</v>
-      </c>
-      <c r="L6" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K7" t="s">
-        <v>20</v>
-      </c>
-      <c r="L7" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L8" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="3">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" t="s">
-        <v>20</v>
       </c>
       <c r="E9" t="s">
         <v>15</v>
       </c>
       <c r="F9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" t="s">
         <v>18</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
         <v>21</v>
       </c>
-      <c r="H9" t="s">
+      <c r="B10" t="s">
         <v>13</v>
       </c>
-      <c r="I9" t="s">
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" t="s">
         <v>16</v>
       </c>
-      <c r="J9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K9" t="s">
+      <c r="H11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" t="s">
         <v>19</v>
       </c>
-      <c r="L9" s="4">
+      <c r="J11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="4" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="3">
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" t="s">
-        <v>21</v>
-      </c>
-      <c r="H10" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" t="s">
-        <v>19</v>
-      </c>
-      <c r="K10" t="s">
-        <v>17</v>
-      </c>
-      <c r="L10" s="4">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="3">
+        <v>22</v>
+      </c>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" t="s">
         <v>20</v>
       </c>
-      <c r="I11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J11" t="s">
-        <v>19</v>
-      </c>
-      <c r="K11" t="s">
-        <v>17</v>
-      </c>
-      <c r="L11" s="4">
-        <v>10</v>
+      <c r="D11" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/vip2022.xlsx
+++ b/data/vip2022.xlsx
@@ -1,29 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/isabelhaas/Documents/Coding/aytogermany/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{046F4D97-A752-7C4E-8CF9-36BEF0CAD47D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="240" yWindow="760" windowWidth="27860" windowHeight="22180" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Candidates" sheetId="1" r:id="rId1"/>
-    <sheet name="Nights" sheetId="2" r:id="rId2"/>
-    <sheet name="Matchboxes" sheetId="3" r:id="rId3"/>
-    <sheet name="Solution" sheetId="4" r:id="rId4"/>
+    <sheet sheetId="1" name="Candidates" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Nights" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Matchboxes" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Solution" state="visible" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="32">
   <si>
     <t>left</t>
   </si>
@@ -103,28 +94,51 @@
     <t>episode</t>
   </si>
   <si>
+    <t>Frau</t>
+  </si>
+  <si>
+    <t>Mann</t>
+  </si>
+  <si>
     <t>result</t>
+  </si>
+  <si>
+    <t>before_night</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>true</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF2C3E50"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF2C3E50"/>
+      <sz val="12"/>
+      <name val="Times"/>
     </font>
   </fonts>
   <fills count="3">
@@ -137,7 +151,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC5C6C7"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -153,17 +166,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -250,6 +269,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -284,6 +304,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -318,20 +339,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -453,20 +470,60 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="3" width="10.6640625" customWidth="1"/>
+    <col min="1" max="3" width="10.714285714285714" customWidth="1"/>
+    <col min="4" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -477,7 +534,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -488,7 +545,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -496,7 +553,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -504,7 +561,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -512,7 +569,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -520,7 +577,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -528,7 +585,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -536,7 +593,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -544,7 +601,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -552,7 +609,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -560,25 +617,27 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="11" width="10.6640625" customWidth="1"/>
+    <col min="1" max="11" width="10.714285714285714" customWidth="1"/>
+    <col min="12" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -613,7 +672,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -648,7 +707,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -683,7 +742,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -718,7 +777,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -753,7 +812,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -788,7 +847,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -823,7 +882,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -858,7 +917,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -893,7 +952,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -928,7 +987,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -965,32 +1024,37 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="4" width="10.6640625" customWidth="1"/>
+    <col min="1" max="4" width="10.714285714285714" customWidth="1"/>
+    <col min="5" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1000,11 +1064,14 @@
       <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1014,11 +1081,14 @@
       <c r="C3" t="s">
         <v>23</v>
       </c>
-      <c r="D3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1028,11 +1098,14 @@
       <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="D4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1042,11 +1115,14 @@
       <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1056,11 +1132,14 @@
       <c r="C6" t="s">
         <v>5</v>
       </c>
-      <c r="D6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1070,11 +1149,14 @@
       <c r="C7" t="s">
         <v>23</v>
       </c>
-      <c r="D7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1084,11 +1166,14 @@
       <c r="C8" t="s">
         <v>4</v>
       </c>
-      <c r="D8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1098,11 +1183,14 @@
       <c r="C9" t="s">
         <v>21</v>
       </c>
-      <c r="D9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1112,11 +1200,14 @@
       <c r="C10" t="s">
         <v>23</v>
       </c>
-      <c r="D10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1126,21 +1217,28 @@
       <c r="C11" t="s">
         <v>19</v>
       </c>
-      <c r="D11" t="b">
-        <v>0</v>
+      <c r="D11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1148,7 +1246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1156,7 +1254,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1164,7 +1262,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1172,7 +1270,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1180,7 +1278,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1188,7 +1286,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1196,7 +1294,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -1204,7 +1302,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1212,7 +1310,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1220,7 +1318,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -1228,7 +1326,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -1237,6 +1335,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>